--- a/output/SMC_allocation_CORRECTED.xlsx
+++ b/output/SMC_allocation_CORRECTED.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1144,74 +1144,90 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Housing and utilities</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Council rates</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>SRS2_ANNUAL_B</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Public Administration and Regulatory Services</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Out of scope - not modelled (leaves the Australian economy, or is a transfer)</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="9" t="n">
         <v>4484.704275988574</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>TRANSFER: a property tax, not a purchase of public administration services. Out of scope for a household consumption shock; model it as government expenditure if you want the councils re-spending captured.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Housing and utilities</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Body corporate</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>SRS2_ANNUAL_C</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>6702</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Non-Residential Property Operators and Real Estate Services</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>1891.439451143153</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Construction Services</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>756.5757804572613</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>REALLOCATED: 6702 has a $16.5m household cell and would strip to almost nothing. Strata fees buy repairs, cleaning and grounds, and building insurance, so they are allocated to those.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1221,110 +1237,126 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>Body corporate</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>SRS2_ANNUAL_C</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>7310</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Building Cleaning, Pest Control and Other Support Services</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>756.5757804572613</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>REALLOCATED: 6702 has a $16.5m household cell and would strip to almost nothing. Strata fees buy repairs, cleaning and grounds, and building insurance, so they are allocated to those.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Housing and utilities</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Body corporate</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>SRS2_ANNUAL_C</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Insurance and Superannuation Funds</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>378.2878902286307</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>REALLOCATED: 6702 has a $16.5m household cell and would strip to almost nothing. Strata fees buy repairs, cleaning and grounds, and building insurance, so they are allocated to those.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Housing and utilities</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>SRS3_ANNUAL_A</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>2605</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Electricity Transmission, Distribution, On Selling and Electricity Market Operation</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G23" s="9" t="n">
         <v>2227.650397124838</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>generation is upstream - households buy from the distributor/retailer</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Housing and utilities</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Gas</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SRS3_ANNUAL_B</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>2701</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Gas Supply</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>777.7391893873245</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Housing and utilities</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SRS3_ANNUAL_C</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Water Supply, Sewerage and Drainage Services</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>1467.288146381483</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1334,29 +1366,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SRS2_ANNUAL_A</t>
+          <t>SRS3_ANNUAL_B</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ownership of Dwellings</t>
+          <t>Gas Supply</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1106.452013878753</v>
+        <v>777.7391893873245</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1364,34 +1396,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Insurance and financial services</t>
+          <t>Housing and utilities</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Building &amp; contents insurance*</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SRS2_ANNUAL_D</t>
+          <t>SRS3_ANNUAL_C</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Insurance and Superannuation Funds</t>
+          <t>Water Supply, Sewerage and Drainage Services</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>2993.692455926287</v>
+        <v>1467.288146381483</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1399,34 +1431,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Insurance and financial services</t>
+          <t>Housing and utilities</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Building &amp; contents insurance*</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SRS2_ANNUAL_D</t>
+          <t>SRS2_ANNUAL_A</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Auxiliary Finance and Insurance Services</t>
+          <t>Ownership of Dwellings</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>332.6324951029209</v>
+        <v>1106.452013878753</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1439,12 +1471,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Health insurance*</t>
+          <t>Building &amp; contents insurance*</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SRS10_ANNUAL_A</t>
+          <t>SRS2_ANNUAL_D</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1461,7 +1493,7 @@
         <v>0.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>4112.404825781184</v>
+        <v>2993.692455926287</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1474,12 +1506,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Health insurance*</t>
+          <t>Building &amp; contents insurance*</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SRS10_ANNUAL_A</t>
+          <t>SRS2_ANNUAL_D</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1496,7 +1528,7 @@
         <v>0.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>456.9338695312426</v>
+        <v>332.6324951029209</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1509,12 +1541,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Motor insurance*</t>
+          <t>Health insurance*</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SRS11D_ANNUAL_B</t>
+          <t>SRS10_ANNUAL_A</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1531,7 +1563,7 @@
         <v>0.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2078.423723333021</v>
+        <v>4112.404825781184</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1544,12 +1576,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Motor insurance*</t>
+          <t>Health insurance*</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SRS11D_ANNUAL_B</t>
+          <t>SRS10_ANNUAL_A</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1566,7 +1598,7 @@
         <v>0.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>230.9359692592246</v>
+        <v>456.9338695312426</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1579,29 +1611,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financial and other services (whole block) (imputed)</t>
+          <t>Motor insurance*</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
+          <t>SRS11D_ANNUAL_B</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Insurance and Superannuation Funds</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1199.047831349623</v>
+        <v>2078.423723333021</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1614,12 +1646,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financial and other services (whole block) (imputed)</t>
+          <t>Motor insurance*</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
+          <t>SRS11D_ANNUAL_B</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1633,10 +1665,10 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>342.585094671321</v>
+        <v>230.9359692592246</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1659,19 +1691,19 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Professional, Scientific and Technical Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>171.2925473356605</v>
+        <v>1199.047831349623</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -1684,7 +1716,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Insurance types never asked (travel, belongings, accident) (imputed)</t>
+          <t>Financial and other services (whole block) (imputed)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1694,19 +1726,19 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Insurance and Superannuation Funds</t>
+          <t>Auxiliary Finance and Insurance Services</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>396.3518479512077</v>
+        <v>342.585094671321</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1719,7 +1751,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Insurance types never asked (travel, belongings, accident) (imputed)</t>
+          <t>Financial and other services (whole block) (imputed)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1729,19 +1761,19 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auxiliary Finance and Insurance Services</t>
+          <t>Professional, Scientific and Technical Services</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>44.03909421680086</v>
+        <v>171.2925473356605</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -1749,34 +1781,34 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Health and aged care</t>
+          <t>Insurance and financial services</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Formal aged care</t>
+          <t>Insurance types never asked (travel, belongings, accident) (imputed)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SRS9_ANNUAL</t>
+          <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Residential Care and Social Assistance Services</t>
+          <t>Insurance and Superannuation Funds</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>280.2435074258621</v>
+        <v>396.3518479512077</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -1784,80 +1816,72 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Health and aged care</t>
+          <t>Insurance and financial services</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Medical procedures</t>
+          <t>Insurance types never asked (travel, belongings, accident) (imputed)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SRS10_ANNUAL_B</t>
+          <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Auxiliary Finance and Insurance Services</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2047.508185081721</v>
+        <v>44.03909421680086</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Health and aged care</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Medicines</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>SRS10_ANNUAL_C</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Human Pharmaceutical and Medicinal Product Manufacturing</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Formal aged care</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SRS9_ANNUAL</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>8601</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Residential Care and Social Assistance Services</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="9" t="n">
-        <v>2145.536737319286</v>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>retail removed</t>
-        </is>
-      </c>
+      <c r="G38" s="5" t="n">
+        <v>280.2435074258621</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1867,12 +1891,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Health care professional</t>
+          <t>Medical procedures</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SRS10_ANNUAL_D</t>
+          <t>SRS10_ANNUAL_B</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1889,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1772.902483995014</v>
+        <v>2047.508185081721</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -1902,29 +1926,29 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Spectacles, hearing aids and therapeutic appliances (imputed)</t>
+          <t>Medicines</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
+          <t>SRS10_ANNUAL_C</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
+          <t>Human Pharmaceutical and Medicinal Product Manufacturing</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>424.5887738506958</v>
+        <v>2145.536737319286</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
@@ -1940,72 +1964,80 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Travel and holidays</t>
+          <t>Health and aged care</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Domestic holidays</t>
+          <t>Health care professional</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SRS12_ANNUAL_F</t>
+          <t>SRS10_ANNUAL_D</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Accommodation</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2373.753516801229</v>
+        <v>1772.902483995014</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Travel and holidays</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Domestic holidays</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>SRS12_ANNUAL_F</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>4901</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Air and Space Transport</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>2077.034327201075</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Health and aged care</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Spectacles, hearing aids and therapeutic appliances (imputed)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Never asked; donor imputed from HES 2015-16</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>424.5887738506958</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>retail removed</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2025,19 +2057,19 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Food and Beverage Services</t>
+          <t>Accommodation</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1483.595948000768</v>
+        <v>2373.753516801229</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2050,12 +2082,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Overseas holidays and non-holiday air fares (imputed)</t>
+          <t>Domestic holidays</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
+          <t>SRS12_ANNUAL_F</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2069,10 +2101,10 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>4045.220548696765</v>
+        <v>2077.034327201075</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2085,137 +2117,161 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Overseas holidays and non-holiday air fares (imputed)</t>
+          <t>Domestic holidays</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
+          <t>SRS12_ANNUAL_F</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Employment, Travel Agency and Other Administrative Services</t>
+          <t>Food and Beverage Services</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>2022.610274348383</v>
+        <v>1483.595948000768</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Travel and holidays</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Overseas holidays and non-holiday air fares (imputed)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>4401</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Accommodation</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>674.2034247827943</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Out of scope - not modelled (leaves the Australian economy, or is a transfer)</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>5393.627398262353</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>OVERSEAS: 80% is consumed overseas or flown on foreign carriers, so it is an import and out of scope. Only the Australian-carrier and Australian-agency share is domestic production.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Communications</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>SRS3_ANNUAL_D</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Telecommunication Services</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>963.7374683985831</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Travel and holidays</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Overseas holidays and non-holiday air fares (imputed)</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Never asked; donor imputed from HES 2015-16</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Air and Space Transport</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>1011.305137174191</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>OVERSEAS: 80% is consumed overseas or flown on foreign carriers, so it is an import and out of scope. Only the Australian-carrier and Australian-agency share is domestic production.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Communications</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>SRS3_ANNUAL_D</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>5701</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>413.0303435993928</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Travel and holidays</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Overseas holidays and non-holiday air fares (imputed)</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Never asked; donor imputed from HES 2015-16</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>7210</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Employment, Travel Agency and Other Administrative Services</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>337.1017123913971</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>OVERSEAS: 80% is consumed overseas or flown on foreign carriers, so it is an import and out of scope. Only the Australian-carrier and Australian-agency share is domestic production.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2225,12 +2281,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mobile phone</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SRS3_ANNUAL_E</t>
+          <t>SRS3_ANNUAL_D</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2244,56 +2300,48 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1125.559111215163</v>
+        <v>963.7374683985831</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Communications</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Mobile phones/tablets*</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>SRS7_ANNUAL_F</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>2401</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="9" t="n">
-        <v>462.5514303288508</v>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>retail removed</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SRS3_ANNUAL_D</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>5701</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>413.0303435993928</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2303,29 +2351,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Postal services (whole block) (imputed)</t>
+          <t>Mobile phone</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
+          <t>SRS3_ANNUAL_E</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Postal and Courier Pick-up and Delivery Service</t>
+          <t>Telecommunication Services</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>124.1792018775694</v>
+        <v>1125.559111215163</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2333,34 +2381,34 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Household goods</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Mobile phones/tablets*</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>SRS7_ANNUAL_A</t>
+          <t>SRS7_ANNUAL_F</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Furniture Manufacturing</t>
+          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>1396.685933095917</v>
+        <v>462.5514303288508</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
@@ -2374,47 +2422,39 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Household goods</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Small appliances</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>SRS7_ANNUAL_B</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Domestic Appliance Manufacturing</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="n">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Communications</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Postal services (whole block) (imputed)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Never asked; donor imputed from HES 2015-16</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Postal and Courier Pick-up and Delivery Service</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="9" t="n">
-        <v>248.5150416841813</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>retail removed</t>
-        </is>
-      </c>
+      <c r="G53" s="5" t="n">
+        <v>124.1792018775694</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2424,29 +2464,29 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Whitegoods</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>SRS7_ANNUAL_C</t>
+          <t>SRS7_ANNUAL_A</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Domestic Appliance Manufacturing</t>
+          <t>Furniture Manufacturing</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>580.3291088956487</v>
+        <v>1396.685933095917</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
@@ -2467,12 +2507,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Other household appliances</t>
+          <t>Small appliances</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>SRS7_ANNUAL_G</t>
+          <t>SRS7_ANNUAL_B</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2489,88 +2529,104 @@
         <v>1</v>
       </c>
       <c r="G55" s="9" t="n">
+        <v>248.5150416841813</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>retail removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Household goods</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Whitegoods</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>SRS7_ANNUAL_C</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Domestic Appliance Manufacturing</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>580.3291088956487</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>retail removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Household goods</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Other household appliances</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>SRS7_ANNUAL_G</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Domestic Appliance Manufacturing</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="9" t="n">
         <v>523.3212566460392</v>
       </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>retail removed</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Household goods</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Domestic cleaning/pest</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>SRS8_ANNUAL_A</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>7310</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Building Cleaning, Pest Control and Other Support Services</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>589.7636775878213</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Household goods</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Music/news/magazines</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>SRS8_ANNUAL_D</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>5401</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Publishing (except Internet and Music Publishing)</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>170.3925358315105</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2580,29 +2636,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Music/news/magazines</t>
+          <t>Domestic cleaning/pest</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SRS8_ANNUAL_D</t>
+          <t>SRS8_ANNUAL_A</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
+          <t>Building Cleaning, Pest Control and Other Support Services</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>102.2355214989063</v>
+        <v>589.7636775878213</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2625,108 +2681,92 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motion Picture and Sound Recording</t>
+          <t>Publishing (except Internet and Music Publishing)</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>68.15701433260422</v>
+        <v>170.3925358315105</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Household goods</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Household textiles, glassware and utensils (whole block) (imputed)</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Textile Product Manufacturing</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G60" s="9" t="n">
-        <v>545.7871180868755</v>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>retail removed, remainder rescaled</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Music/news/magazines</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SRS8_ANNUAL_D</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>5701</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>102.2355214989063</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Household goods</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Household textiles, glassware and utensils (whole block) (imputed)</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Glass and Glass Product Manufacturing</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>545.7871180868755</v>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>retail removed, remainder rescaled</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Music/news/magazines</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SRS8_ANNUAL_D</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Motion Picture and Sound Recording</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>68.15701433260422</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -2736,7 +2776,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Tools and equipment for house and garden (whole block) (imputed)</t>
+          <t>Household textiles, glassware and utensils (whole block) (imputed)</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -2746,19 +2786,19 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Other Fabricated Metal Product manufacturing</t>
+          <t>Textile Product Manufacturing</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>578.8758187790045</v>
+        <v>545.7871180868755</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
@@ -2779,7 +2819,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Tools and equipment for house and garden (whole block) (imputed)</t>
+          <t>Household textiles, glassware and utensils (whole block) (imputed)</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -2789,19 +2829,19 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Specialised and other Machinery and Equipment Manufacturing</t>
+          <t>Glass and Glass Product Manufacturing</t>
         </is>
       </c>
       <c r="F63" s="8" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>347.3254912674026</v>
+        <v>545.7871180868755</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
@@ -2822,7 +2862,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Books and stationery (imputed)</t>
+          <t>Tools and equipment for house and garden (whole block) (imputed)</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -2832,19 +2872,19 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Publishing (except Internet and Music Publishing)</t>
+          <t>Other Fabricated Metal Product manufacturing</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
         <v>0.625</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>244.5955436871912</v>
+        <v>578.8758187790045</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
@@ -2865,7 +2905,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Books and stationery (imputed)</t>
+          <t>Tools and equipment for house and garden (whole block) (imputed)</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -2875,19 +2915,19 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Paper Stationery and Other Converted Paper Product Manufacturing</t>
+          <t>Specialised and other Machinery and Equipment Manufacturing</t>
         </is>
       </c>
       <c r="F65" s="8" t="n">
         <v>0.375</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>146.7573262123147</v>
+        <v>347.3254912674026</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
@@ -2908,7 +2948,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Routine maintenance never asked (garden services, cleaning and paper goods) (imputed)</t>
+          <t>Books and stationery (imputed)</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -2918,19 +2958,19 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Building Cleaning, Pest Control and Other Support Services</t>
+          <t>Publishing (except Internet and Music Publishing)</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>0.8</v>
+        <v>0.625</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>849.8622525148153</v>
+        <v>244.5955436871912</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
@@ -2951,7 +2991,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Routine maintenance never asked (garden services, cleaning and paper goods) (imputed)</t>
+          <t>Books and stationery (imputed)</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -2970,10 +3010,10 @@
         </is>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>212.4655631287038</v>
+        <v>146.7573262123147</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
@@ -2989,34 +3029,34 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Personal care and services</t>
+          <t>Household goods</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Cosmetic/personal care*</t>
+          <t>Routine maintenance never asked (garden services, cleaning and paper goods) (imputed)</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>SRS8_ANNUAL_B</t>
+          <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Cleaning Compounds and Toiletry Preparation Manufacturing</t>
+          <t>Building Cleaning, Pest Control and Other Support Services</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>1174.834641686929</v>
+        <v>849.8622525148153</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
@@ -3025,44 +3065,52 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>retail removed</t>
+          <t>retail removed, remainder rescaled</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Personal care and services</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Hairdressing/beauty*</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>SRS8_ANNUAL_C</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>9501</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Personal Services</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>1466.289175969144</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Household goods</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Routine maintenance never asked (garden services, cleaning and paper goods) (imputed)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Never asked; donor imputed from HES 2015-16</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Paper Stationery and Other Converted Paper Product Manufacturing</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>212.4655631287038</v>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>retail removed, remainder rescaled</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -3072,29 +3120,29 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Personal effects (whole block) (imputed)</t>
+          <t>Cosmetic/personal care*</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
+          <t>SRS8_ANNUAL_B</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Other Manufactured Products</t>
+          <t>Cleaning Compounds and Toiletry Preparation Manufacturing</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>1325.398324478534</v>
+        <v>1174.834641686929</v>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
@@ -3108,160 +3156,168 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Recreation and leisure</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>TV/home theatre*</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>SRS7_ANNUAL_D</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>2401</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="n">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Personal care and services</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hairdressing/beauty*</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SRS8_ANNUAL_C</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>9501</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Personal Services</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="9" t="n">
-        <v>379.819171370922</v>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>retail removed</t>
-        </is>
-      </c>
+      <c r="G71" s="5" t="n">
+        <v>1466.289175969144</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Recreation and leisure</t>
+          <t>Personal care and services</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Computers*</t>
+          <t>Personal effects (whole block) (imputed)</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>SRS7_ANNUAL_E</t>
+          <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
+          <t>Other Manufactured Products</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="9" t="n">
+        <v>1325.398324478534</v>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>retail removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Recreation and leisure</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>TV/home theatre*</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>SRS7_ANNUAL_D</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>379.819171370922</v>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>retail removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Recreation and leisure</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Computers*</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>SRS7_ANNUAL_E</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="9" t="n">
         <v>397.1274146923103</v>
       </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>retail removed</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Recreation and leisure</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>TV streaming</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>SRS12_ANNUAL_A</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>5701</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>478.2058030738061</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Recreation and leisure</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>TV streaming</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>SRS12_ANNUAL_A</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>5501</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Motion Picture and Sound Recording</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>318.8038687158707</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3271,12 +3327,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Music streaming</t>
+          <t>TV streaming</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SRS12_ANNUAL_B</t>
+          <t>SRS12_ANNUAL_A</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -3293,7 +3349,7 @@
         <v>0.6</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>53.59052350528311</v>
+        <v>478.2058030738061</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -3306,12 +3362,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Music streaming</t>
+          <t>TV streaming</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SRS12_ANNUAL_B</t>
+          <t>SRS12_ANNUAL_A</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -3328,7 +3384,7 @@
         <v>0.4</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>35.72701567018874</v>
+        <v>318.8038687158707</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -3341,29 +3397,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gyms/sporting clubs</t>
+          <t>Music streaming</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SRS12_ANNUAL_C</t>
+          <t>SRS12_ANNUAL_B</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sports and Recreation</t>
+          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1229.815685460185</v>
+        <v>53.59052350528311</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3376,12 +3432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cinema/theatre/concerts</t>
+          <t>Music streaming</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SRS12_ANNUAL_D</t>
+          <t>SRS12_ANNUAL_B</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -3395,10 +3451,10 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>333.4232695307155</v>
+        <v>35.72701567018874</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -3411,29 +3467,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cinema/theatre/concerts</t>
+          <t>Gyms/sporting clubs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SRS12_ANNUAL_D</t>
+          <t>SRS12_ANNUAL_C</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heritage, Creative and Performing Arts</t>
+          <t>Sports and Recreation</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>333.4232695307155</v>
+        <v>1229.815685460185</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3446,220 +3502,220 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sporting events</t>
+          <t>Cinema/theatre/concerts</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SRS12_ANNUAL_E</t>
+          <t>SRS12_ANNUAL_D</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sports and Recreation</t>
+          <t>Motion Picture and Sound Recording</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>228.6641587612276</v>
+        <v>333.4232695307155</v>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Recreation and leisure</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cinema/theatre/concerts</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SRS12_ANNUAL_D</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>8901</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Heritage, Creative and Performing Arts</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>333.4232695307155</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Recreation and leisure</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sporting events</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SRS12_ANNUAL_E</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Sports and Recreation</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>228.6641587612276</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Recreation and leisure</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Pets, gardens and recreation durables (whole block) (imputed)</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>0103</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>Other Agriculture</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F83" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G81" s="9" t="n">
+      <c r="G83" s="9" t="n">
         <v>1388.331436064138</v>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>retail removed, remainder rescaled</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Recreation and leisure</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Pets, gardens and recreation durables (whole block) (imputed)</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>2502</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>Other Manufactured Products</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n">
+      <c r="F84" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G82" s="9" t="n">
+      <c r="G84" s="9" t="n">
         <v>1388.331436064138</v>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>retail removed, remainder rescaled</t>
         </is>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Recreation and leisure</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Gambling (lotto, TAB, pokies, casino) (imputed)</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>9201</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Gambling</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>802.7641808388698</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Car lease</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>SRS11D_ANNUAL_A</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>6601</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Rental and Hiring Services (except Real Estate)</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>187.8079113108857</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Recreation and leisure</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vehicle registration</t>
+          <t>Gambling (lotto, TAB, pokies, casino) (imputed)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SRS11D_ANNUAL_C</t>
+          <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Public Administration and Regulatory Services</t>
+          <t>Gambling</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1428.601752373048</v>
+        <v>802.7641808388698</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
@@ -3672,67 +3728,75 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Taxis/rideshare</t>
+          <t>Car lease</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SRS11D_ANNUAL_D</t>
+          <t>SRS11D_ANNUAL_A</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Rental and Hiring Services (except Real Estate)</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>183.6132222929587</v>
+        <v>187.8079113108857</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Public transport</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>SRS11D_ANNUAL_E</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>4601</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Road Transport</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>73.2385037170386</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Vehicle registration</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>SRS11D_ANNUAL_C</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Out of scope - not modelled (leaves the Australian economy, or is a transfer)</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="9" t="n">
+        <v>1428.601752373048</v>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>TRANSFER: predominantly a registration tax. Out of scope. If you have the split, the CTP insurance component could be returned to 6301.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3742,118 +3806,102 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Public transport</t>
+          <t>Taxis/rideshare</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SRS11D_ANNUAL_E</t>
+          <t>SRS11D_ANNUAL_D</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>73.2385037170386</v>
+        <v>183.6132222929587</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Vehicle operation (fuel, servicing, parts, tolls, parking) (imputed)</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>Petroleum and Coal Product Manufacturing</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="G89" s="9" t="n">
-        <v>3323.95530818284</v>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>retail removed, remainder rescaled</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Public transport</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SRS11D_ANNUAL_E</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Road Transport</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>73.2385037170386</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Vehicle operation (fuel, servicing, parts, tolls, parking) (imputed)</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Never asked; donor imputed from HES 2015-16</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>9401</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Automotive Repair and Maintenance</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="G90" s="9" t="n">
-        <v>2912.358590846879</v>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>retail removed, remainder rescaled</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Public transport</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SRS11D_ANNUAL_E</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>4701</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Rail Transport</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>73.2385037170386</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -3863,29 +3911,29 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Motor vehicle purchase (gross outlay, not annualised)</t>
+          <t>Vehicle operation (fuel, servicing, parts, tolls, parking) (imputed)</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>SRS11C_1_OTHER (mean-imputed where bought, amount missing)</t>
+          <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Motor Vehicles and Parts; Other Transport Equipment manufacturing</t>
+          <t>Petroleum and Coal Product Manufacturing</t>
         </is>
       </c>
       <c r="F91" s="8" t="n">
-        <v>1</v>
+        <v>0.533</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>8290.436848224539</v>
+        <v>3323.95530818284</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
@@ -3894,41 +3942,41 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>retail removed</t>
+          <t>retail removed, remainder rescaled</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Clothing and footwear</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Clothing &amp; footwear</t>
+          <t>Vehicle operation (fuel, servicing, parts, tolls, parking) (imputed)</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>SRS6_ANNUAL</t>
+          <t>Never asked; donor imputed from HES 2015-16</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Clothing Manufacturing</t>
+          <t>Automotive Repair and Maintenance</t>
         </is>
       </c>
       <c r="F92" s="8" t="n">
-        <v>0.714</v>
+        <v>0.467</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>2549.602087474573</v>
+        <v>2912.358590846879</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
@@ -3944,34 +3992,34 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Clothing and footwear</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Clothing &amp; footwear</t>
+          <t>Motor vehicle purchase (gross outlay, not annualised)</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>SRS6_ANNUAL</t>
+          <t>SRS11C_1_OTHER (mean-imputed where bought, amount missing)</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Footwear Manufacturing</t>
+          <t>Motor Vehicles and Parts; Other Transport Equipment manufacturing</t>
         </is>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>1021.269183498218</v>
+        <v>8290.436848224539</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
@@ -3980,122 +4028,138 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>retail removed, remainder rescaled</t>
+          <t>retail removed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
+          <t>Clothing and footwear</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Clothing &amp; footwear</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>SRS6_ANNUAL</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Clothing Manufacturing</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="G94" s="9" t="n">
+        <v>2549.602087474573</v>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>retail removed, remainder rescaled</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Clothing and footwear</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Clothing &amp; footwear</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>SRS6_ANNUAL</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Footwear Manufacturing</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="G95" s="9" t="n">
+        <v>1021.269183498218</v>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>retail removed, remainder rescaled</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
           <t>Other (tobacco and education)</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Tobacco</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>SRS5_ANNUAL</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>1205</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Wine, Spirits and Tobacco</t>
         </is>
       </c>
-      <c r="F94" s="8" t="n">
+      <c r="F96" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G94" s="9" t="n">
+      <c r="G96" s="9" t="n">
         <v>242.0428121272097</v>
       </c>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr">
         <is>
           <t>retail removed</t>
         </is>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Other (tobacco and education)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>SRS13_ANNUAL</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>8110</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Technical, Vocational and Tertiary Education Services (incl undergraduate and postgraduate)</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>137.3951143645482</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Other (tobacco and education)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>SRS13_ANNUAL</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>8010</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Primary and Secondary Education Services (incl Pre-Schools and Special Schools)</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>82.43706861872892</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4115,61 +4179,131 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arts, Sports, Adult and Other Education Services (incl community education)</t>
+          <t>Technical, Vocational and Tertiary Education Services (incl undergraduate and postgraduate)</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>54.95804574581928</v>
+        <v>137.3951143645482</v>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Other (tobacco and education)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SRS13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Primary and Secondary Education Services (incl Pre-Schools and Special Schools)</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>82.43706861872892</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Other (tobacco and education)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SRS13_ANNUAL</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Arts, Sports, Adult and Other Education Services (incl community education)</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>54.95804574581928</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>Home improvements</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Home improvements/repairs</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>SRS2_ANNUAL_E</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>3201</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>Construction Services</t>
         </is>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F100" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G98" s="9" t="n">
+      <c r="G100" s="9" t="n">
         <v>12703.65324308109</v>
       </c>
-      <c r="H98" s="6" t="inlineStr">
+      <c r="H100" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>retail removed; 3001 is new-dwelling GFCF with a near-empty household cell, so repairs and improvements go to construction services</t>
         </is>
@@ -4186,7 +4320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4265,1756 +4399,1783 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Construction Services</t>
+          <t>Out of scope - not modelled (leaves the Australian economy, or is a transfer)</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>7622.191945848654</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>12703.65324308109</v>
+        <v>11306.93342662397</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>5081.461297232436</v>
+        <v>11306.93342662397</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.06290707418529169</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.1048451236421528</v>
+        <v>0.09331778902054325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Motor Vehicles and Parts; Other Transport Equipment manufacturing</t>
+          <t>Public Administration and Regulatory Services</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4559.740266523497</v>
+        <v>5913.306028361622</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>8290.436848224539</v>
+        <v>0</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>3730.696581701042</v>
+        <v>-5913.306028361622</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.03763220885142884</v>
+        <v>0.04880338669627401</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.0684221979116888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Residential Building Construction</t>
+          <t>Construction Services</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3175.913310770272</v>
+        <v>7622.191945848654</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>13460.22902353835</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-3175.913310770272</v>
+        <v>5838.037077689698</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.0262112809105382</v>
+        <v>0.06290707418529169</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>0.111089255131644</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meat and meat product manufacturing</t>
+          <t>Motor Vehicles and Parts; Other Transport Equipment manufacturing</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>4559.740266523497</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2746.690640316981</v>
+        <v>8290.436848224539</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>2746.690640316981</v>
+        <v>3730.696581701042</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>0.03763220885142884</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.02266884291316921</v>
+        <v>0.06842219791168878</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dairy product manufacturing</t>
+          <t>Residential Building Construction</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
+        <v>3175.913310770272</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>2028.962432796966</v>
-      </c>
       <c r="E7" s="10" t="n">
-        <v>2028.962432796966</v>
+        <v>-3175.913310770272</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>0.0262112809105382</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.01674532617203957</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other Manufactured Products</t>
+          <t>Air and Space Transport</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>814.1189281628017</v>
+        <v>6122.254875897841</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2713.729760542672</v>
+        <v>3088.339464375267</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1899.610832379871</v>
+        <v>-3033.915411522574</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.006719043573480277</v>
+        <v>0.05052787234899378</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.02239681191160093</v>
+        <v>0.02548852104159232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bakery product manufacturing</t>
+          <t>Meat and meat product manufacturing</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1794.320518800038</v>
+        <v>2746.690640316981</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1794.320518800038</v>
+        <v>2746.690640316981</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.01480879185282411</v>
+        <v>0.02266884291316921</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clothing Manufacturing</t>
+          <t>Dairy product manufacturing</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>892.717817743198</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2549.602087474573</v>
+        <v>2028.962432796966</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1656.884269731375</v>
+        <v>2028.962432796966</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.007367731800284703</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02104224202161311</v>
+        <v>0.01674532617203956</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sheep, Grains, Beef and Dairy Cattle</t>
+          <t>Other Manufactured Products</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1380.246552923106</v>
+        <v>814.1189281628017</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>2713.729760542672</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>-1380.246552923106</v>
+        <v>1899.610832379871</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.01139137834832624</v>
+        <v>0.006719043573480277</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>0.02239681191160092</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other Food Product Manufacturing</t>
+          <t>Non-Residential Property Operators and Real Estate Services</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3450.616382307765</v>
+        <v>1891.439451143153</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2111.777225972352</v>
+        <v>0</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>-1338.839156335413</v>
+        <v>-1891.439451143153</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.02847844587081559</v>
+        <v>0.01561032872372804</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.01742880887293914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Soft drinks, cordials and syrup manufacturing</t>
+          <t>Bakery product manufacturing</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1325.036690806182</v>
+        <v>1794.320518800038</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>1325.036690806182</v>
+        <v>1794.320518800038</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.01093572321439319</v>
+        <v>0.01480879185282411</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Human Pharmaceutical and Medicinal Product Manufacturing</t>
+          <t>Employment, Travel Agency and Other Administrative Services</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>858.2146949277145</v>
+        <v>2022.610274348383</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2145.536737319286</v>
+        <v>337.1017123913971</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1287.322042391572</v>
+        <v>-1685.508561956985</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.007082972439460684</v>
+        <v>0.01669290087160097</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.01770743109865171</v>
+        <v>0.002782150145266828</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fruit and vegetable product manufacturing</t>
+          <t>Clothing Manufacturing</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>892.717817743198</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1214.616966572333</v>
+        <v>2549.602087474573</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1214.616966572333</v>
+        <v>1656.884269731375</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>0.007367731800284703</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01002441294652709</v>
+        <v>0.02104224202161311</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wine, Spirits and Tobacco</t>
+          <t>Sheep, Grains, Beef and Dairy Cattle</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>800.3465468853009</v>
+        <v>1380.246552923106</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1883.411392656935</v>
+        <v>0</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1083.064845771634</v>
+        <v>-1380.246552923106</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.006605378079763115</v>
+        <v>0.01139137834832624</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.01554407197313133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sugar and confectionery manufacturing</t>
+          <t>Other Food Product Manufacturing</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>3450.616382307765</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1021.382449163098</v>
+        <v>2111.777225972352</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>1021.382449163098</v>
+        <v>-1338.839156335413</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0</v>
+        <v>0.02847844587081559</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.008429619977761415</v>
+        <v>0.01742880887293914</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
+          <t>Soft drinks, cordials and syrup manufacturing</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>685.4910868317271</v>
+        <v>0</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1664.086790242779</v>
+        <v>1325.036690806182</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>978.5957034110519</v>
+        <v>1325.036690806182</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.005657459030032137</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.01373395368527564</v>
+        <v>0.01093572321439319</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>0103</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other Agriculture</t>
+          <t>Human Pharmaceutical and Medicinal Product Manufacturing</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>416.4994308192415</v>
+        <v>858.2146949277145</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1388.331436064138</v>
+        <v>2145.536737319286</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>971.8320052448969</v>
+        <v>1287.322042391572</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.003437431224353745</v>
+        <v>0.007082972439460684</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.01145810408117915</v>
+        <v>0.01770743109865171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Electricity Generation</t>
+          <t>Fruit and vegetable product manufacturing</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>891.0601588499353</v>
+        <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>1214.616966572333</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>1214.616966572333</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>-891.0601588499353</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.007354050896981136</v>
-      </c>
       <c r="G20" s="4" t="n">
-        <v>0</v>
+        <v>0.01002441294652709</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Electricity Transmission, Distribution, On Selling and Electricity Market Operation</t>
+          <t>Wine, Spirits and Tobacco</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1336.590238274903</v>
+        <v>800.3465468853009</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2227.650397124838</v>
+        <v>1883.411392656935</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>891.0601588499353</v>
+        <v>1083.064845771634</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.0110310763454717</v>
+        <v>0.006605378079763115</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.01838512724245284</v>
+        <v>0.01554407197313132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Petroleum and Coal Product Manufacturing</t>
+          <t>Sugar and confectionery manufacturing</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>2494.525559611888</v>
+        <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>3323.95530818284</v>
+        <v>1021.382449163098</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>829.4297485709521</v>
+        <v>1021.382449163098</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.0205876873149433</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.02743309334716194</v>
+        <v>0.008429619977761413</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Domestic Appliance Manufacturing</t>
+          <t>Professional, Scientific, Computer and Electronic Equipment Manufacturing</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>569.8826183351301</v>
+        <v>685.4910868317271</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1352.165407225869</v>
+        <v>1664.086790242779</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>782.2827888907392</v>
+        <v>978.5957034110519</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.004703325290573591</v>
+        <v>0.005657459030032137</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.01115962051171781</v>
+        <v>0.01373395368527564</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>0103</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Furniture Manufacturing</t>
+          <t>Other Agriculture</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>628.5086698931628</v>
+        <v>416.4994308192415</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1396.685933095917</v>
+        <v>1388.331436064138</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>768.1772632027545</v>
+        <v>971.8320052448969</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.005187174739754745</v>
+        <v>0.003437431224353745</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.01152705497723277</v>
+        <v>0.01145810408117915</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grain mill and cereal product manufacturing</t>
+          <t>Building Cleaning, Pest Control and Other Support Services</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>1227.160366973933</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>759.1356041077084</v>
+        <v>2196.201710559898</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>759.1356041077084</v>
+        <v>969.0413435859653</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>0.01012793547983576</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.006265258091579431</v>
+        <v>0.0181255765944469</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Automotive Repair and Maintenance</t>
+          <t>Electricity Transmission, Distribution, On Selling and Electricity Market Operation</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>2182.709864660401</v>
+        <v>1336.590238274903</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>2912.358590846879</v>
+        <v>2227.650397124838</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>729.6487261864772</v>
+        <v>891.0601588499353</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.01801422640057538</v>
+        <v>0.0110310763454717</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0240361249401963</v>
+        <v>0.01838512724245284</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cleaning Compounds and Toiletry Preparation Manufacturing</t>
+          <t>Electricity Generation</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>469.9338566747716</v>
+        <v>891.0601588499353</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1174.834641686929</v>
+        <v>0</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>704.9007850121574</v>
+        <v>-891.0601588499353</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.003878433420995231</v>
+        <v>0.007354050896981136</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.009696083552488079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Footwear Manufacturing</t>
+          <t>Petroleum and Coal Product Manufacturing</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>357.0871270972792</v>
+        <v>2494.525559611888</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1021.269183498218</v>
+        <v>3323.95530818284</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>664.1820564009392</v>
+        <v>829.4297485709521</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.002947092720113881</v>
+        <v>0.0205876873149433</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.008428685179525702</v>
+        <v>0.02743309334716194</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Processed seafood manufacturing</t>
+          <t>Domestic Appliance Manufacturing</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0</v>
+        <v>569.8826183351301</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>538.2961556400114</v>
+        <v>1352.165407225869</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>538.2961556400114</v>
+        <v>782.2827888907392</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0</v>
+        <v>0.004703325290573591</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.004442637555847233</v>
+        <v>0.01115962051171781</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other Fabricated Metal Product manufacturing</t>
+          <t>Furniture Manufacturing</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>231.5503275116018</v>
+        <v>628.5086698931628</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>578.8758187790045</v>
+        <v>1396.685933095917</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>347.3254912674027</v>
+        <v>768.1772632027545</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.001911019000031116</v>
+        <v>0.005187174739754745</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.004777547500077791</v>
+        <v>0.01152705497723276</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Textile Product Manufacturing</t>
+          <t>Grain mill and cereal product manufacturing</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>218.3148472347502</v>
+        <v>0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>545.7871180868755</v>
+        <v>759.1356041077084</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>327.4722708521252</v>
+        <v>759.1356041077084</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.001801784629449916</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.004504461573624791</v>
+        <v>0.006265258091579429</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Glass and Glass Product Manufacturing</t>
+          <t>Automotive Repair and Maintenance</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>218.3148472347502</v>
+        <v>2182.709864660401</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>545.7871180868755</v>
+        <v>2912.358590846879</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>327.4722708521252</v>
+        <v>729.6487261864772</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.001801784629449916</v>
+        <v>0.01801422640057538</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.004504461573624791</v>
+        <v>0.02403612494019629</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oils and fats manufacturing</t>
+          <t>Cleaning Compounds and Toiletry Preparation Manufacturing</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0</v>
+        <v>469.9338566747716</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>262.2468450553902</v>
+        <v>1174.834641686929</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>262.2468450553902</v>
+        <v>704.9007850121574</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>0.003878433420995231</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.002164361886181985</v>
+        <v>0.009696083552488076</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Building Cleaning, Pest Control and Other Support Services</t>
+          <t>Accommodation</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>1227.160366973933</v>
+        <v>3047.956941584023</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1439.625930102637</v>
+        <v>2373.753516801229</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>212.4655631287039</v>
+        <v>-674.2034247827942</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.01012793547983576</v>
+        <v>0.02515523812572432</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.01188144510495568</v>
+        <v>0.01959093783519067</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Specialised and other Machinery and Equipment Manufacturing</t>
+          <t>Footwear Manufacturing</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>138.9301965069611</v>
+        <v>357.0871270972792</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>347.3254912674026</v>
+        <v>1021.269183498218</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>208.3952947604416</v>
+        <v>664.1820564009392</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.00114661140001867</v>
+        <v>0.002947092720113881</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.002866528500046674</v>
+        <v>0.008428685179525698</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Publishing (except Internet and Music Publishing)</t>
+          <t>Processed seafood manufacturing</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>268.230753306387</v>
+        <v>0</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>414.9880795187017</v>
+        <v>538.2961556400114</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>146.7573262123148</v>
+        <v>538.2961556400114</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.002213747963433484</v>
+        <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.003424957819189123</v>
+        <v>0.004442637555847231</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Paper Stationery and Other Converted Paper Product Manufacturing</t>
+          <t>Insurance and Superannuation Funds</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>218.0521028314537</v>
+        <v>9580.872852991701</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>359.2228893410185</v>
+        <v>9959.160743220331</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>141.1707865095648</v>
+        <v>378.2878902286302</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.001799616161142195</v>
+        <v>0.07907235656158632</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.002964719480875558</v>
+        <v>0.08219442230633191</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Beer Manufacturing</t>
+          <t>Other Fabricated Metal Product manufacturing</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>444.8153334768904</v>
+        <v>231.5503275116018</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>582.7080868547264</v>
+        <v>578.8758187790045</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>137.892753377836</v>
+        <v>347.3254912674027</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.003671126544776417</v>
+        <v>0.001911019000031116</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.004809175773657108</v>
+        <v>0.00477754750007779</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Glass and Glass Product Manufacturing</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1199.047831349623</v>
+        <v>218.3148472347502</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1199.047831349623</v>
+        <v>545.7871180868755</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>327.4722708521252</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.009895918577530085</v>
+        <v>0.001801784629449916</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.009895918577530086</v>
+        <v>0.00450446157362479</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Employment, Travel Agency and Other Administrative Services</t>
+          <t>Textile Product Manufacturing</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2022.610274348383</v>
+        <v>218.3148472347502</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2022.610274348383</v>
+        <v>545.7871180868755</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>327.4722708521252</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.01669290087160097</v>
+        <v>0.001801784629449916</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.01669290087160097</v>
+        <v>0.00450446157362479</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Professional, Scientific and Technical Services</t>
+          <t>Oils and fats manufacturing</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>171.2925473356605</v>
+        <v>0</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>171.2925473356605</v>
+        <v>262.2468450553902</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>262.2468450553902</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.00141370265393287</v>
+        <v>0</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.00141370265393287</v>
+        <v>0.002164361886181985</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Food and Beverage Services</t>
+          <t>Specialised and other Machinery and Equipment Manufacturing</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>8008.773072721531</v>
+        <v>138.9301965069611</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>8008.773072721531</v>
+        <v>347.3254912674026</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0</v>
+        <v>208.3952947604416</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.06609758523507846</v>
+        <v>0.00114661140001867</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.06609758523507846</v>
+        <v>0.002866528500046673</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
+          <t>Publishing (except Internet and Music Publishing)</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>73.2385037170386</v>
+        <v>268.230753306387</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>73.2385037170386</v>
+        <v>414.9880795187017</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0</v>
+        <v>146.7573262123148</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.0006044481717699043</v>
+        <v>0.002213747963433484</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.0006044481717699044</v>
+        <v>0.003424957819189122</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gas Supply</t>
+          <t>Paper Stationery and Other Converted Paper Product Manufacturing</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>777.7391893873245</v>
+        <v>218.0521028314537</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>777.7391893873245</v>
+        <v>359.2228893410185</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0</v>
+        <v>141.1707865095648</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.006418796224391028</v>
+        <v>0.001799616161142195</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.006418796224391029</v>
+        <v>0.002964719480875557</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Accommodation</t>
+          <t>Beer Manufacturing</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>3047.956941584023</v>
+        <v>444.8153334768904</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>3047.956941584023</v>
+        <v>582.7080868547264</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>137.892753377836</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.02515523812572432</v>
+        <v>0.003671126544776417</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.02515523812572433</v>
+        <v>0.004809175773657106</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Telecommunication Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2089.296579613746</v>
+        <v>1199.047831349623</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2089.296579613746</v>
+        <v>1199.047831349623</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.01724327278328656</v>
+        <v>0.009895918577530085</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.01724327278328656</v>
+        <v>0.009895918577530085</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Health Care Services</t>
+          <t>Professional, Scientific and Technical Services</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>3820.410669076735</v>
+        <v>171.2925473356605</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>3820.410669076735</v>
+        <v>171.2925473356605</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.03153041265364404</v>
+        <v>0.00141370265393287</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.03153041265364404</v>
+        <v>0.00141370265393287</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Auxiliary Finance and Insurance Services</t>
+          <t>Gambling</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1407.12652278151</v>
+        <v>802.7641808388698</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1407.12652278151</v>
+        <v>802.7641808388698</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.01161322270359755</v>
+        <v>0.006625331169314064</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.01161322270359755</v>
+        <v>0.006625331169314063</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Air and Space Transport</t>
+          <t>Ownership of Dwellings</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>6122.254875897841</v>
+        <v>1106.452013878753</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>6122.254875897841</v>
+        <v>1106.452013878753</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.05052787234899378</v>
+        <v>0.009131711640697399</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>0.05052787234899378</v>
+        <v>0.009131711640697397</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
+          <t>Food and Beverage Services</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>1047.062191677388</v>
+        <v>8008.773072721531</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>1047.062191677388</v>
+        <v>8008.773072721531</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.00864155867976241</v>
+        <v>0.06609758523507846</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.008641558679762412</v>
+        <v>0.06609758523507844</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Personal Services</t>
+          <t>Rental and Hiring Services (except Real Estate)</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1466.289175969144</v>
+        <v>187.8079113108857</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1466.289175969144</v>
+        <v>187.8079113108857</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.01210150080516126</v>
+        <v>0.001550006388366168</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0.01210150080516126</v>
+        <v>0.001550006388366168</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Health Care Services</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>256.8517260099973</v>
+        <v>3820.410669076735</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>256.8517260099973</v>
+        <v>3820.410669076735</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.002119835173073972</v>
+        <v>0.03153041265364404</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0.002119835173073972</v>
+        <v>0.03153041265364403</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Water Supply, Sewerage and Drainage Services</t>
+          <t>Arts, Sports, Adult and Other Education Services (incl community education)</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>1467.288146381483</v>
+        <v>54.95804574581928</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1467.288146381483</v>
+        <v>54.95804574581928</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.01210974545529398</v>
+        <v>0.0004535768562865781</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0.01210974545529398</v>
+        <v>0.000453576856286578</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Technical, Vocational and Tertiary Education Services (incl undergraduate and postgraduate)</t>
+          <t>Postal and Courier Pick-up and Delivery Service</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>137.3951143645482</v>
+        <v>238.4724825966622</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>137.3951143645482</v>
+        <v>238.4724825966622</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.001133942140716445</v>
+        <v>0.001968148566768825</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>0.001133942140716445</v>
+        <v>0.001968148566768825</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gambling</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>802.7641808388698</v>
+        <v>256.8517260099973</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>802.7641808388698</v>
+        <v>256.8517260099973</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.006625331169314064</v>
+        <v>0.002119835173073972</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0.006625331169314064</v>
+        <v>0.002119835173073972</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Residential Care and Social Assistance Services</t>
+          <t>Auxiliary Finance and Insurance Services</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>280.2435074258621</v>
+        <v>1407.12652278151</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>280.2435074258621</v>
+        <v>1407.12652278151</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.002312890994720575</v>
+        <v>0.01161322270359755</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0.002312890994720576</v>
+        <v>0.01161322270359755</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Heritage, Creative and Performing Arts</t>
+          <t>Personal Services</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>333.4232695307155</v>
+        <v>1466.289175969144</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>333.4232695307155</v>
+        <v>1466.289175969144</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.002751791413872077</v>
+        <v>0.01210150080516126</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>0.002751791413872077</v>
+        <v>0.01210150080516126</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Non-Residential Property Operators and Real Estate Services</t>
+          <t>Heritage, Creative and Performing Arts</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1891.439451143153</v>
+        <v>333.4232695307155</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>1891.439451143153</v>
+        <v>333.4232695307155</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.01561032872372804</v>
+        <v>0.002751791413872077</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>0.01561032872372804</v>
+        <v>0.002751791413872077</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Public Administration and Regulatory Services</t>
+          <t>Internet Service Providers, Internet Publishing and Broadcasting, Websearch Portals and Data Processing</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>5913.306028361622</v>
+        <v>1047.062191677388</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>5913.306028361622</v>
+        <v>1047.062191677388</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.04880338669627401</v>
+        <v>0.00864155867976241</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>0.04880338669627402</v>
+        <v>0.00864155867976241</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rental and Hiring Services (except Real Estate)</t>
+          <t>Gas Supply</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>187.8079113108857</v>
+        <v>777.7391893873245</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>187.8079113108857</v>
+        <v>777.7391893873245</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.001550006388366168</v>
+        <v>0.006418796224391028</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>0.001550006388366168</v>
+        <v>0.006418796224391028</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Arts, Sports, Adult and Other Education Services (incl community education)</t>
+          <t>Motion Picture and Sound Recording</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>54.95804574581928</v>
+        <v>756.1111682493791</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>54.95804574581928</v>
+        <v>756.1111682493791</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0.0004535768562865781</v>
+        <v>0.006240296976422497</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>0.0004535768562865781</v>
+        <v>0.006240296976422496</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sports and Recreation</t>
+          <t>Primary and Secondary Education Services (incl Pre-Schools and Special Schools)</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>1458.479844221413</v>
+        <v>82.43706861872892</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>1458.479844221413</v>
+        <v>82.43706861872892</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.01203704923859324</v>
+        <v>0.0006803652844298671</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0.01203704923859324</v>
+        <v>0.0006803652844298671</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Motion Picture and Sound Recording</t>
+          <t>Residential Care and Social Assistance Services</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>756.1111682493791</v>
+        <v>280.2435074258621</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>756.1111682493791</v>
+        <v>280.2435074258621</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.006240296976422497</v>
+        <v>0.002312890994720575</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>0.006240296976422498</v>
+        <v>0.002312890994720575</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Primary and Secondary Education Services (incl Pre-Schools and Special Schools)</t>
+          <t>Rail Transport</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>82.43706861872892</v>
+        <v>73.2385037170386</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>82.43706861872892</v>
+        <v>73.2385037170386</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.0006803652844298671</v>
+        <v>0.0006044481717699043</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>0.0006803652844298672</v>
+        <v>0.0006044481717699042</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Postal and Courier Pick-up and Delivery Service</t>
+          <t>Sports and Recreation</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>238.4724825966622</v>
+        <v>1458.479844221413</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>238.4724825966622</v>
+        <v>1458.479844221413</v>
       </c>
       <c r="E65" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.001968148566768825</v>
+        <v>0.01203704923859324</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.001968148566768826</v>
+        <v>0.01203704923859324</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ownership of Dwellings</t>
+          <t>Water Supply, Sewerage and Drainage Services</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1106.452013878753</v>
+        <v>1467.288146381483</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1106.452013878753</v>
+        <v>1467.288146381483</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.009131711640697399</v>
+        <v>0.01210974545529398</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.009131711640697399</v>
+        <v>0.01210974545529398</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Insurance and Superannuation Funds</t>
+          <t>Telecommunication Services</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>9580.872852991701</v>
+        <v>2089.296579613746</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>9580.872852991701</v>
+        <v>2089.296579613746</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0.07907235656158632</v>
+        <v>0.01724327278328656</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0.07907235656158633</v>
+        <v>0.01724327278328656</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Technical, Vocational and Tertiary Education Services (incl undergraduate and postgraduate)</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>137.3951143645482</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>137.3951143645482</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.001133942140716445</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0.001133942140716445</v>
       </c>
     </row>
   </sheetData>
@@ -6028,22 +6189,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>What changed</t>
+          <t>WHAT CHANGED</t>
         </is>
       </c>
       <c r="B1" s="12" t="inlineStr"/>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Retail and wholesale removed</t>
@@ -6051,11 +6212,11 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>The model strips the retail and wholesale margin out of the purchasers price and reallocates it to 3901 and 3301 itself. Allocating to retail as well counted it twice. On $100 of groceries the original split gave retail $72.85 against a correct $22.43, and food manufacturing $20.54 against $58.69.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>The model strips the retail and wholesale margin out of the purchasers price and reallocates it to 3901 and 3301 itself. Allocating to retail as well counted it twice. On $100 of groceries the original split gave retail $72.85 against a correct $22.43, and food manufacturing $20.54 against $58.69. After the fix, retail lands at 12.3% of the direct vector - exactly its share of ABS household consumption. Before, it was 31.5%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="39" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Groceries and alcohol</t>
@@ -6063,11 +6224,11 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Split across the food manufacturing codes using ABS household purchasers-price spend on each product, rather than judgement. Note 1205 bundles wine, spirits AND tobacco, so it is overstated as an alcohol proxy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>Split across food manufacturing codes using ABS household purchasers-price spend per product, not judgement. Note 1205 bundles wine, spirits AND tobacco, so it overstates as an alcohol proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Electricity</t>
@@ -6075,11 +6236,11 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Was 60% distribution / 40% generation. Households buy from the distributor-retailer (2605); generation is upstream and the multiplier reaches it. Splitting it manually double-counted the supply chain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>Was 60% distribution / 40% generation. Households buy from the distributor-retailer (2605); generation is upstream and the multiplier reaches it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Home improvements</t>
@@ -6087,7 +6248,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Was 60/25/15 across construction services, residential building construction and retail. 3001 is NEW DWELLING construction, which is capital formation, not household consumption - its ABS household cell is $58m. All of it now goes to 3201 Construction services.</t>
+          <t>3001 is NEW DWELLING construction - capital formation, not household consumption, with a $58m household cell. All to 3201.</t>
         </is>
       </c>
     </row>
@@ -6098,80 +6259,128 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>STILL TO DECIDE - not changed here</t>
+          <t>OUT OF SCOPE - your decisions this round</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="65" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Overseas holidays</t>
+          <t>Overseas holidays: 80% out</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>US$6.7bn is allocated to Australian air transport and travel agencies. Spending consumed overseas is an import and does not stimulate the domestic economy. Only the Australian-carrier and Australian-agency portion should be in the shock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>Most of an overseas trip is consumed overseas or flown on a foreign carrier, which is an import and does not stimulate the Australian economy. 15% stays with Australian air transport and 5% with Australian travel agencies. The 80/15/5 split is JUDGEMENT - roughly a third of a trip is airfare and Australian carriers hold about a third of international capacity. Replace it if you have carrier or destination data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Council rates and vehicle registration</t>
+          <t>Council rates: 100% out</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>$5.9bn to 7501 Public administration. These are largely taxes and transfers rather than purchases of public administration services, and the ABS household cell for 7501 is only $1,053m.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>A property tax, not a purchase of public administration services. The ABS household cell for 7501 is only $1,112m, which is the tell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Body corporate</t>
+          <t>Vehicle registration: 100% out</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>$1.9bn to 6702, whose ABS household cell is effectively zero. The strip will be unreliable; consider 3201 or 7310 for the services actually bought.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>Predominantly a registration tax. If you have the split, the CTP insurance component could be returned to 6301.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Note on the two above</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>6301 is Insurance AND SUPERANNUATION FUNDS. $9.6bn of super-funded spending routed back into the superannuation industry is circular.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>The money is not lost to the economy - councils and states spend it. Capturing that needs a separate GOVERNMENT expenditure shock, not a household consumption one. Excluding it here avoids attributing an industry multiplier to a tax payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Body corporate: reallocated</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>6701 gets 0.9% of the shock against 24.6% of ABS household consumption. Most retirees own outright, so their housing is imputed rent (6700) which the supplied data lacks - but 0.9% still looks low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Aged care</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>8601 gets 0.23% against 2.60% of ABS household consumption, which looks low for a retiree population.</t>
+          <t>6702 has a $16.5m household cell and would strip to almost nothing. Strata fees buy repairs (3201), cleaning and grounds (7310) and building insurance (6301), so they now go there 40/40/20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="11" t="inlineStr"/>
+      <c r="B13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>KEPT IN, WITH A CAVEAT</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15" ht="91" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Insurance stays in 6301</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>This is a MEASUREMENT BASIS issue, not circularity. Your survey measures insurance on a cash-outlay basis - gross premiums - but 70-85% of a premium is the claims pool, which is a transfer rather than production. Allocating the whole premium to 6301 attributes to insurance money that actually ends up with panel beaters, builders and health providers. The total spend is real, so removing it would understate; the INDUSTRY attribution is what is approximate. Disclose that the insurance industry impact is overstated. 6301 also bundles insurers with superannuation funds, which blends the multiplier - an approximation, not an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Rent and aged care left as surveyed</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Rent gets 0.9% of the shock against 24.6% of ABS household consumption, and aged care 0.23% against 2.60%. Both look low for a retiree population, but the survey data stands as collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="11" t="inlineStr"/>
+      <c r="B17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>STILL INDICATIVE</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Concordance status</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>These are judgement weights, not the ABS concordance. The authoritative source is Industry and Product Concordance Tables 2023-24.xlsx from the ABS Input-Output METHODOLOGY page. Every weight here belongs in the limitations section until that is used.</t>
         </is>
       </c>
     </row>
